--- a/data/trans_orig/P36BPD08_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de vasos de vino que consumen a la semana en 2023</t>
+          <t>Población según el número de vasos de vino que consumen a la semana en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>333436</t>
+          <t>334923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>375934</t>
+          <t>376337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>312053</t>
+          <t>312351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>646288</t>
+          <t>645391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>687123</t>
+          <t>689217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54849</t>
+          <t>54221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55733</t>
+          <t>54836</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>23653</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>849</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369952</t>
+          <t>370796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397176</t>
+          <t>398061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480708</t>
+          <t>480646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500440</t>
+          <t>500663</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>857028</t>
+          <t>858159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>894122</t>
+          <t>894315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25725</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30966</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>24946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56296</t>
+          <t>54578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>481577</t>
+          <t>479122</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>506321</t>
+          <t>505548</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>513372</t>
+          <t>513122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>528607</t>
+          <t>527847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1002172</t>
+          <t>1001851</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1031835</t>
+          <t>1030606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25214</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37950</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37126</t>
+          <t>37966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26397</t>
+          <t>26802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48520</t>
+          <t>48266</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>794825</t>
+          <t>796789</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>858897</t>
+          <t>858294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>678343</t>
+          <t>677924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>694034</t>
+          <t>694121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1488532</t>
+          <t>1488308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1549367</t>
+          <t>1543844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>31412</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24450</t>
+          <t>23686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48425</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16698</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>60534</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29308</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>67189</t>
+          <t>65585</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>457009</t>
+          <t>457073</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>490175</t>
+          <t>488442</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>519881</t>
+          <t>520374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>533216</t>
+          <t>533304</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>982451</t>
+          <t>981603</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1016795</t>
+          <t>1017513</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>28387</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50397</t>
+          <t>51580</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>37368</t>
+          <t>38293</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>62636</t>
+          <t>63833</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60528</t>
+          <t>60286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43775</t>
+          <t>43210</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71482</t>
+          <t>70225</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>257957</t>
+          <t>258284</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285959</t>
+          <t>285307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>571771</t>
+          <t>570117</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>600348</t>
+          <t>598533</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>819933</t>
+          <t>819625</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>919646</t>
+          <t>915395</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22387</t>
+          <t>22696</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41220</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60373</t>
+          <t>58602</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53008</t>
+          <t>53706</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76004</t>
+          <t>76145</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>98363</t>
+          <t>99067</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>214122</t>
+          <t>213763</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>235647</t>
+          <t>234803</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>411417</t>
+          <t>411637</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>419909</t>
+          <t>419856</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>629369</t>
+          <t>628771</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>652623</t>
+          <t>652405</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>24345</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>16357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49824</t>
+          <t>50625</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>34923</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54527</t>
+          <t>54943</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2977203</t>
+          <t>2980225</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3127482</t>
+          <t>3136197</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3522376</t>
+          <t>3522576</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3567345</t>
+          <t>3567237</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3987,17 +3987,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6577630</t>
+          <t>6577631</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6520156</t>
+          <t>6521436</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6651074</t>
+          <t>6649045</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>118028</t>
+          <t>123873</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>194280</t>
+          <t>196118</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>47191</t>
+          <t>49209</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>75865</t>
+          <t>76199</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>184075</t>
+          <t>185455</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>256138</t>
+          <t>259999</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>199087</t>
+          <t>196775</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>293360</t>
+          <t>292243</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>41912</t>
+          <t>42223</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>69937</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>266346</t>
+          <t>267560</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>348439</t>
+          <t>350513</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7111232</t>
+          <t>7111233</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7111232</t>
+          <t>7111233</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7111232</t>
+          <t>7111233</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">

--- a/data/trans_orig/P36BPD08_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>358219</t>
+          <t>367861</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>334923</t>
+          <t>345730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>376337</t>
+          <t>382824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>313036</t>
+          <t>360249</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>312351</t>
+          <t>350399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>671255</t>
+          <t>728111</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>645391</t>
+          <t>704613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>689217</t>
+          <t>746165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30041</t>
+          <t>26787</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54221</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>30041</t>
+          <t>26787</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54836</t>
+          <t>48340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>27285</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>385303</t>
+          <t>433760</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370796</t>
+          <t>414072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398061</t>
+          <t>446410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>491721</t>
+          <t>478299</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480646</t>
+          <t>468003</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500663</t>
+          <t>487010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>877025</t>
+          <t>912060</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>858159</t>
+          <t>889184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>894315</t>
+          <t>926859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>35338</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -1407,102 +1407,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>28912</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38852</t>
+          <t>43433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14864</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7602</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23693</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>43776</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>31203</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>60622</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>6,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14082</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6716</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24946</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>40315</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>26167</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>54578</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>422340</t>
+          <t>475713</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>422340</t>
+          <t>475713</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422340</t>
+          <t>475713</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>500017</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>500017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>500017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>933682</t>
+          <t>975730</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933682</t>
+          <t>975730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>933682</t>
+          <t>975730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>494670</t>
+          <t>573401</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>479122</t>
+          <t>558066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>505548</t>
+          <t>584990</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>521853</t>
+          <t>598778</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>513122</t>
+          <t>589105</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>527847</t>
+          <t>605792</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1016523</t>
+          <t>1172179</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1001851</t>
+          <t>1154199</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1030606</t>
+          <t>1186445</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1863,27 +1863,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>31309</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>21313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37966</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36201</t>
+          <t>41963</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26802</t>
+          <t>30325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48266</t>
+          <t>57147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>825448</t>
+          <t>633490</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>796789</t>
+          <t>616014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>858294</t>
+          <t>647670</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>686853</t>
+          <t>708626</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>677924</t>
+          <t>699777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>694121</t>
+          <t>716115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1512301</t>
+          <t>1342117</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1488308</t>
+          <t>1322196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1543844</t>
+          <t>1359374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>19178</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>29419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23686</t>
+          <t>25173</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>35018</t>
+          <t>36523</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>26908</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48721</t>
+          <t>48438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40356</t>
+          <t>44747</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60534</t>
+          <t>60589</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>49969</t>
+          <t>55270</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>42543</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65585</t>
+          <t>70774</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>884789</t>
+          <t>697415</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>884789</t>
+          <t>697415</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>884789</t>
+          <t>697415</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1597287</t>
+          <t>1433910</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1597287</t>
+          <t>1433910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1597287</t>
+          <t>1433910</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>473725</t>
+          <t>516549</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>457073</t>
+          <t>497278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>488442</t>
+          <t>531352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>527724</t>
+          <t>586008</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>520374</t>
+          <t>578156</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>533304</t>
+          <t>592153</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1001448</t>
+          <t>1102557</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>981603</t>
+          <t>1083566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1017513</t>
+          <t>1118528</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38299</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>28900</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51580</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15914</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>48719</t>
+          <t>51586</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38293</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>63833</t>
+          <t>66612</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>47221</t>
+          <t>51313</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36214</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60286</t>
+          <t>66451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,17 +2810,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>55826</t>
+          <t>60882</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43210</t>
+          <t>47975</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70225</t>
+          <t>75287</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>559244</t>
+          <t>607328</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>559244</t>
+          <t>607328</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>559244</t>
+          <t>607328</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>546750</t>
+          <t>607697</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546750</t>
+          <t>607697</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546750</t>
+          <t>607697</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1105994</t>
+          <t>1215025</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1105994</t>
+          <t>1215025</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1105994</t>
+          <t>1215025</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>271720</t>
+          <t>299546</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>258284</t>
+          <t>283644</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>285307</t>
+          <t>313514</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>585775</t>
+          <t>413295</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>570117</t>
+          <t>404753</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>598533</t>
+          <t>419428</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>857495</t>
+          <t>712841</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>819625</t>
+          <t>694461</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>915395</t>
+          <t>729903</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30006</t>
+          <t>33818</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>24931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>44201</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23440</t>
+          <t>20720</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>48129</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19635</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58602</t>
+          <t>60851</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>64297</t>
+          <t>71353</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53706</t>
+          <t>60199</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76145</t>
+          <t>84719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>82914</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>68677</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99067</t>
+          <t>98629</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>366023</t>
+          <t>404717</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>366023</t>
+          <t>404717</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>366023</t>
+          <t>404717</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>974391</t>
+          <t>843883</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>974391</t>
+          <t>843883</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>974391</t>
+          <t>843883</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>225093</t>
+          <t>247477</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>213763</t>
+          <t>233819</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>234803</t>
+          <t>257925</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>416490</t>
+          <t>453481</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>411637</t>
+          <t>447899</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>419856</t>
+          <t>457658</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>641584</t>
+          <t>700958</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>628771</t>
+          <t>687411</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>652405</t>
+          <t>713272</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>27944</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,47 +3629,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>25482</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>18178</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>35225</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>22783</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>16357</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>30994</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>43258</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32121</t>
+          <t>34202</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>53549</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,17 +3757,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>43682</t>
+          <t>47764</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34923</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54943</t>
+          <t>59957</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>464006</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>464006</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425290</t>
+          <t>464006</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>774204</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>774204</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>774204</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3034178</t>
+          <t>3072085</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2980225</t>
+          <t>3027867</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3136197</t>
+          <t>3108403</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3543453</t>
+          <t>3598737</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3522576</t>
+          <t>3577598</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3567237</t>
+          <t>3616682</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6577631</t>
+          <t>6670822</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6521436</t>
+          <t>6618733</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6649045</t>
+          <t>6716431</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>160392</t>
+          <t>166761</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>123873</t>
+          <t>139503</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>196118</t>
+          <t>197903</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>61456</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>49209</t>
+          <t>56763</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>76199</t>
+          <t>83019</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>221848</t>
+          <t>236118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>185455</t>
+          <t>207006</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>259999</t>
+          <t>271017</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>256747</t>
+          <t>284037</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>196775</t>
+          <t>255306</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>292243</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>55007</t>
+          <t>63938</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>70939</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>311754</t>
+          <t>347975</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>267560</t>
+          <t>314030</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>350513</t>
+          <t>385890</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3451317</t>
+          <t>3522883</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3451317</t>
+          <t>3522883</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3451317</t>
+          <t>3522883</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3659916</t>
+          <t>3732032</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3659916</t>
+          <t>3732032</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3659916</t>
+          <t>3732032</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7111233</t>
+          <t>7254915</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7111233</t>
+          <t>7254915</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7111233</t>
+          <t>7254915</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
